--- a/infrastructure/knowledgebase/SystemData.xlsx
+++ b/infrastructure/knowledgebase/SystemData.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10714"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\user1\sense\use-case-template\infrastructure\knowledgebase\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wu-my.sharepoint.com/personal/katrin_schreiberhuber_wu_ac_at/Documents/01_Research/Explanation_Generation/SENSE/use-case-template/infrastructure/knowledgebase/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B3F4AA-CF00-40FA-9607-685D7CA17467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="218" documentId="13_ncr:1_{09B3F4AA-CF00-40FA-9607-685D7CA17467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{094FFEE5-F1D3-8046-A71B-DE20113BF3EE}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="28300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlatformTypes" sheetId="1" r:id="rId1"/>
     <sheet name="SensorTypes" sheetId="2" r:id="rId2"/>
-    <sheet name="1_StateTypes" sheetId="3" r:id="rId3"/>
-    <sheet name="1_StateTypeCausality" sheetId="4" r:id="rId4"/>
-    <sheet name="2_EventStateMapping" sheetId="5" r:id="rId5"/>
-    <sheet name="Sensors" sheetId="6" r:id="rId6"/>
-    <sheet name="Platforms" sheetId="7" r:id="rId7"/>
+    <sheet name="Platforms" sheetId="7" r:id="rId3"/>
+    <sheet name="Sensors" sheetId="6" r:id="rId4"/>
+    <sheet name="1_StateTypes" sheetId="3" r:id="rId5"/>
+    <sheet name="2_EventStateMapping" sheetId="5" r:id="rId6"/>
+    <sheet name="1_StateTypeCausality" sheetId="4" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'1_StateTypeCausality'!$A$1:$G$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'1_StateTypeCausality'!$A$1:$G$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -75,6 +75,192 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Unbekannter Autor</author>
+    <author>tc={09D8B89D-83C7-0A4D-A20A-A968FD3B7817}</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Comment:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">    Priorities
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Prio1
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Prio2
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Prio3
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Prio4
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="1" shapeId="0" xr:uid="{09D8B89D-83C7-0A4D-A20A-A968FD3B7817}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Added as there was no connetion between eventTypes and sensors yet.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Comment:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">    @TU: please check and extend if necessary</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Unbekannter Autor</author>
   </authors>
   <commentList>
     <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
@@ -96,53 +282,8 @@
 </comments>
 </file>
 
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Unbekannter Autor</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Priorities
-Prio1
-Prio2
-Prio3
-Prio4
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000002000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    @TU: please check and extend if necessary</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="179">
   <si>
     <t>PlatformType</t>
   </si>
@@ -162,9 +303,6 @@
     <t>StateType</t>
   </si>
   <si>
-    <t>SensorType_possible</t>
-  </si>
-  <si>
     <t>TriggerExplanation_State</t>
   </si>
   <si>
@@ -217,13 +355,478 @@
   </si>
   <si>
     <t>Platform</t>
+  </si>
+  <si>
+    <t>household4</t>
+  </si>
+  <si>
+    <t>household5</t>
+  </si>
+  <si>
+    <t>household6</t>
+  </si>
+  <si>
+    <t>household7</t>
+  </si>
+  <si>
+    <t>household8</t>
+  </si>
+  <si>
+    <t>household9</t>
+  </si>
+  <si>
+    <t>household10</t>
+  </si>
+  <si>
+    <t>household11</t>
+  </si>
+  <si>
+    <t>household12</t>
+  </si>
+  <si>
+    <t>household13</t>
+  </si>
+  <si>
+    <t>household14</t>
+  </si>
+  <si>
+    <t>household15</t>
+  </si>
+  <si>
+    <t>household16</t>
+  </si>
+  <si>
+    <t>household17</t>
+  </si>
+  <si>
+    <t>household18</t>
+  </si>
+  <si>
+    <t>household19</t>
+  </si>
+  <si>
+    <t>household20</t>
+  </si>
+  <si>
+    <t>household21</t>
+  </si>
+  <si>
+    <t>household22</t>
+  </si>
+  <si>
+    <t>household23</t>
+  </si>
+  <si>
+    <t>household24</t>
+  </si>
+  <si>
+    <t>household25</t>
+  </si>
+  <si>
+    <t>household26</t>
+  </si>
+  <si>
+    <t>household27</t>
+  </si>
+  <si>
+    <t>household28</t>
+  </si>
+  <si>
+    <t>household29</t>
+  </si>
+  <si>
+    <t>household30</t>
+  </si>
+  <si>
+    <t>household31</t>
+  </si>
+  <si>
+    <t>household32</t>
+  </si>
+  <si>
+    <t>household33</t>
+  </si>
+  <si>
+    <t>household34</t>
+  </si>
+  <si>
+    <t>household35</t>
+  </si>
+  <si>
+    <t>household36</t>
+  </si>
+  <si>
+    <t>household37</t>
+  </si>
+  <si>
+    <t>household38</t>
+  </si>
+  <si>
+    <t>household39</t>
+  </si>
+  <si>
+    <t>household40</t>
+  </si>
+  <si>
+    <t>household41</t>
+  </si>
+  <si>
+    <t>household42</t>
+  </si>
+  <si>
+    <t>household43</t>
+  </si>
+  <si>
+    <t>household44</t>
+  </si>
+  <si>
+    <t>household45</t>
+  </si>
+  <si>
+    <t>household46</t>
+  </si>
+  <si>
+    <t>household47</t>
+  </si>
+  <si>
+    <t>household48</t>
+  </si>
+  <si>
+    <t>household49</t>
+  </si>
+  <si>
+    <t>household50</t>
+  </si>
+  <si>
+    <t>household51</t>
+  </si>
+  <si>
+    <t>household52</t>
+  </si>
+  <si>
+    <t>household53</t>
+  </si>
+  <si>
+    <t>household54</t>
+  </si>
+  <si>
+    <t>household55</t>
+  </si>
+  <si>
+    <t>household56</t>
+  </si>
+  <si>
+    <t>household57</t>
+  </si>
+  <si>
+    <t>household58</t>
+  </si>
+  <si>
+    <t>household59</t>
+  </si>
+  <si>
+    <t>household60</t>
+  </si>
+  <si>
+    <t>household61</t>
+  </si>
+  <si>
+    <t>household62</t>
+  </si>
+  <si>
+    <t>household63</t>
+  </si>
+  <si>
+    <t>household64</t>
+  </si>
+  <si>
+    <t>household65</t>
+  </si>
+  <si>
+    <t>household66</t>
+  </si>
+  <si>
+    <t>household67</t>
+  </si>
+  <si>
+    <t>household68</t>
+  </si>
+  <si>
+    <t>household69</t>
+  </si>
+  <si>
+    <t>household70</t>
+  </si>
+  <si>
+    <t>household71</t>
+  </si>
+  <si>
+    <t>household72</t>
+  </si>
+  <si>
+    <t>household73</t>
+  </si>
+  <si>
+    <t>household74</t>
+  </si>
+  <si>
+    <t>household75</t>
+  </si>
+  <si>
+    <t>household76</t>
+  </si>
+  <si>
+    <t>household77</t>
+  </si>
+  <si>
+    <t>household78</t>
+  </si>
+  <si>
+    <t>household79</t>
+  </si>
+  <si>
+    <t>household80</t>
+  </si>
+  <si>
+    <t>household81</t>
+  </si>
+  <si>
+    <t>household82</t>
+  </si>
+  <si>
+    <t>household83</t>
+  </si>
+  <si>
+    <t>household84</t>
+  </si>
+  <si>
+    <t>household85</t>
+  </si>
+  <si>
+    <t>household86</t>
+  </si>
+  <si>
+    <t>household87</t>
+  </si>
+  <si>
+    <t>household88</t>
+  </si>
+  <si>
+    <t>household89</t>
+  </si>
+  <si>
+    <t>household90</t>
+  </si>
+  <si>
+    <t>household91</t>
+  </si>
+  <si>
+    <t>household92</t>
+  </si>
+  <si>
+    <t>household93</t>
+  </si>
+  <si>
+    <t>household94</t>
+  </si>
+  <si>
+    <t>household95</t>
+  </si>
+  <si>
+    <t>household96</t>
+  </si>
+  <si>
+    <t>household97</t>
+  </si>
+  <si>
+    <t>household98</t>
+  </si>
+  <si>
+    <t>household99</t>
+  </si>
+  <si>
+    <t>household100</t>
+  </si>
+  <si>
+    <t>household101</t>
+  </si>
+  <si>
+    <t>household102</t>
+  </si>
+  <si>
+    <t>household103</t>
+  </si>
+  <si>
+    <t>household104</t>
+  </si>
+  <si>
+    <t>household105</t>
+  </si>
+  <si>
+    <t>household106</t>
+  </si>
+  <si>
+    <t>household107</t>
+  </si>
+  <si>
+    <t>household108</t>
+  </si>
+  <si>
+    <t>household109</t>
+  </si>
+  <si>
+    <t>household110</t>
+  </si>
+  <si>
+    <t>household111</t>
+  </si>
+  <si>
+    <t>household112</t>
+  </si>
+  <si>
+    <t>household113</t>
+  </si>
+  <si>
+    <t>household114</t>
+  </si>
+  <si>
+    <t>household115</t>
+  </si>
+  <si>
+    <t>household116</t>
+  </si>
+  <si>
+    <t>household117</t>
+  </si>
+  <si>
+    <t>household118</t>
+  </si>
+  <si>
+    <t>household119</t>
+  </si>
+  <si>
+    <t>household120</t>
+  </si>
+  <si>
+    <t>household121</t>
+  </si>
+  <si>
+    <t>household122</t>
+  </si>
+  <si>
+    <t>household123</t>
+  </si>
+  <si>
+    <t>household124</t>
+  </si>
+  <si>
+    <t>household125</t>
+  </si>
+  <si>
+    <t>household126</t>
+  </si>
+  <si>
+    <t>household127</t>
+  </si>
+  <si>
+    <t>household128</t>
+  </si>
+  <si>
+    <t>household129</t>
+  </si>
+  <si>
+    <t>household130</t>
+  </si>
+  <si>
+    <t>household131</t>
+  </si>
+  <si>
+    <t>household132</t>
+  </si>
+  <si>
+    <t>household133</t>
+  </si>
+  <si>
+    <t>household134</t>
+  </si>
+  <si>
+    <t>household135</t>
+  </si>
+  <si>
+    <t>household136</t>
+  </si>
+  <si>
+    <t>household137</t>
+  </si>
+  <si>
+    <t>household138</t>
+  </si>
+  <si>
+    <t>household139</t>
+  </si>
+  <si>
+    <t>household140</t>
+  </si>
+  <si>
+    <t>household141</t>
+  </si>
+  <si>
+    <t>household142</t>
+  </si>
+  <si>
+    <t>household143</t>
+  </si>
+  <si>
+    <t>household144</t>
+  </si>
+  <si>
+    <t>household145</t>
+  </si>
+  <si>
+    <t>household146</t>
+  </si>
+  <si>
+    <t>household147</t>
+  </si>
+  <si>
+    <t>household148</t>
+  </si>
+  <si>
+    <t>household149</t>
+  </si>
+  <si>
+    <t>household150</t>
+  </si>
+  <si>
+    <t>household151</t>
+  </si>
+  <si>
+    <t>household152</t>
+  </si>
+  <si>
+    <t>household153</t>
+  </si>
+  <si>
+    <t>household154</t>
+  </si>
+  <si>
+    <t>household155</t>
+  </si>
+  <si>
+    <t>household156</t>
+  </si>
+  <si>
+    <t>household157</t>
+  </si>
+  <si>
+    <t>SensorType_associated</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -262,10 +865,34 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="2" tint="-0.249977111117893"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -288,7 +915,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -302,7 +929,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -386,6 +1017,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Schreiberhuber, Katrin" id="{CE6926BB-C9BE-8A48-9527-C0157D9F0173}" userId="S::katrin.schreiberhuber@wu.ac.at::a8bbfc8c-fdf4-4b40-89d7-e571648d1de5" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -561,19 +1198,27 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="B1" dT="2024-08-05T14:54:41.70" personId="{CE6926BB-C9BE-8A48-9527-C0157D9F0173}" id="{09D8B89D-83C7-0A4D-A20A-A968FD3B7817}">
+    <text>Added as there was no connetion between eventTypes and sensors yet.</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="23.44140625" customWidth="1"/>
+    <col min="2" max="2" width="23.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -581,11 +1226,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Unknown PlatformType" error="Please select an existing PlatformType as the superclass of this PlatformType." sqref="B2:B299" xr:uid="{10849591-1767-044B-BCD4-95D6B0A4162B}">
+      <formula1>$A:$A</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -597,13 +1247,13 @@
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.33203125" customWidth="1"/>
-    <col min="2" max="2" width="24.77734375" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -611,161 +1261,4603 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3"/>
     </row>
-    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3"/>
     </row>
-    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3"/>
     </row>
-    <row r="6" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="18" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="17" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Unknown SensorType" error="Please select an existing SensorTypes as the superclass of this SensorType." sqref="B2:B127" xr:uid="{E593E66C-02DF-7545-8A26-0E94C121F87C}">
+      <formula1>$A:$A</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFC5E0B4"/>
+  </sheetPr>
+  <dimension ref="A1:C160"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="2" max="2" width="11.5" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C7" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C8" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C9" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C10" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C11" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C12" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C13" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C14" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="3"/>
+      <c r="C15" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C16" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C17" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C18" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C19" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C20" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C21" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C22" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C23" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C24" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C25" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C26" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C27" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C28" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C29" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C30" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C31" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C32" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C33" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C34" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="35" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C35" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="36" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C36" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="37" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C37" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="38" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C38" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C39" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="40" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C40" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="41" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C41" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="42" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C42" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="43" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C43" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="44" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C44" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="45" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C45" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="46" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C46" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="47" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C47" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C48" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="49" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C49" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="50" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C50" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="51" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C51" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="52" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C52" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="53" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C53" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="54" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C54" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="55" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C55" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="56" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C56" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="57" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C57" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="58" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C58" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="59" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C59" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="60" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C60" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="61" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C61" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="62" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C62" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="63" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C63" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="64" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C64" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="65" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C65" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="66" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C66" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="67" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C67" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="68" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C68" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="69" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C69" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="70" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C70" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="71" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C71" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="72" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C72" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="73" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C73" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="74" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C74" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="75" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C75" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="76" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C76" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="77" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C77" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="78" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C78" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="79" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C79" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="80" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C80" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="81" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C81" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="82" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C82" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="83" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C83" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C84" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="85" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C85" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="86" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C86" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="87" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C87" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="88" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C88" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="89" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C89" s="7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="90" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C90" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="91" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C91" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="92" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C92" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="93" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C93" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="94" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C94" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="95" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C95" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="96" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C96" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="97" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C97" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="98" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C98" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="99" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C99" s="7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="100" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C100" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="101" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C101" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="102" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C102" s="7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="103" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C103" s="7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="104" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C104" s="7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="105" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C105" s="7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="106" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C106" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="107" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C107" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="108" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C108" s="7" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="109" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C109" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="110" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C110" s="7" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="111" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C111" s="7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="112" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C112" s="7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="113" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C113" s="7" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="114" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C114" s="7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="115" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C115" s="7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="116" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C116" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="117" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C117" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="118" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C118" s="7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="119" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C119" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="120" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C120" s="7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="121" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C121" s="7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="122" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C122" s="7" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="123" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C123" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="124" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C124" s="7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="125" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C125" s="7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="126" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C126" s="7" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="127" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C127" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="128" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C128" s="7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="129" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C129" s="7" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="130" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C130" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="131" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C131" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="132" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C132" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="133" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C133" s="7" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="134" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C134" s="7" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="135" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C135" s="7" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="136" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C136" s="7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="137" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C137" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="138" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C138" s="7" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="139" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C139" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="140" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C140" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="141" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C141" s="7" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="142" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C142" s="7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="143" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C143" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="144" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C144" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="145" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C145" s="7" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="146" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C146" s="7" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="147" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C147" s="7" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="148" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C148" s="7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="149" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C149" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="150" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C150" s="7" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="151" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C151" s="7" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="152" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C152" s="7" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="153" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C153" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="154" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C154" s="7" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="155" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C155" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="156" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C156" s="7" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="157" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C157" s="7" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="158" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C158" s="7" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="159" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C159" s="7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="160" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C160" s="7" t="s">
+        <v>177</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Unknown Platform" error="Please define a Platform, before you use it as a host-platform." sqref="C2:C160" xr:uid="{5268C9C2-08CF-FC48-B553-A68F530C091B}">
+      <formula1>$A:$A</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="PlatformType unknown" error="Please check in the Tab PlaformTypes, if this plaform type was defined correctly before you use it for defining an instance." xr:uid="{BDE253CE-3E02-E24E-9238-87A316C3A068}">
+          <x14:formula1>
+            <xm:f>PlatformTypes!$A:$A</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B360</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFC5E0B4"/>
+  </sheetPr>
+  <dimension ref="A1:E368"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="28.33203125" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" customWidth="1"/>
+    <col min="3" max="3" width="18.5" customWidth="1"/>
+    <col min="4" max="4" width="28.6640625" customWidth="1"/>
+    <col min="5" max="5" width="58.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="E2" s="8"/>
+    </row>
+    <row r="3" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="E3" s="8"/>
+    </row>
+    <row r="4" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="E4" s="8"/>
+    </row>
+    <row r="5" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="E5" s="8"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+    </row>
+    <row r="20" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+    </row>
+    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+    </row>
+    <row r="71" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+    </row>
+    <row r="72" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+    </row>
+    <row r="83" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+    </row>
+    <row r="85" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B85" s="3"/>
+      <c r="C85" s="3"/>
+    </row>
+    <row r="86" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B86" s="3"/>
+      <c r="C86" s="3"/>
+    </row>
+    <row r="87" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B87" s="3"/>
+      <c r="C87" s="3"/>
+    </row>
+    <row r="88" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B88" s="3"/>
+      <c r="C88" s="3"/>
+    </row>
+    <row r="89" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B89" s="3"/>
+      <c r="C89" s="3"/>
+    </row>
+    <row r="90" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B90" s="3"/>
+      <c r="C90" s="3"/>
+    </row>
+    <row r="91" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
+    </row>
+    <row r="92" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+    </row>
+    <row r="93" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B93" s="3"/>
+      <c r="C93" s="3"/>
+    </row>
+    <row r="94" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
+    </row>
+    <row r="95" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+    </row>
+    <row r="96" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B96" s="3"/>
+      <c r="C96" s="3"/>
+    </row>
+    <row r="97" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B97" s="3"/>
+      <c r="C97" s="3"/>
+    </row>
+    <row r="98" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B98" s="3"/>
+      <c r="C98" s="3"/>
+    </row>
+    <row r="99" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B99" s="3"/>
+      <c r="C99" s="3"/>
+    </row>
+    <row r="100" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B100" s="3"/>
+      <c r="C100" s="3"/>
+    </row>
+    <row r="101" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
+    </row>
+    <row r="102" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B102" s="3"/>
+      <c r="C102" s="3"/>
+    </row>
+    <row r="103" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B103" s="3"/>
+      <c r="C103" s="3"/>
+    </row>
+    <row r="104" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B104" s="3"/>
+      <c r="C104" s="3"/>
+    </row>
+    <row r="105" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B105" s="3"/>
+      <c r="C105" s="3"/>
+    </row>
+    <row r="106" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B106" s="3"/>
+      <c r="C106" s="3"/>
+    </row>
+    <row r="107" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B107" s="3"/>
+      <c r="C107" s="3"/>
+    </row>
+    <row r="108" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B108" s="3"/>
+      <c r="C108" s="3"/>
+    </row>
+    <row r="109" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B109" s="3"/>
+      <c r="C109" s="3"/>
+    </row>
+    <row r="110" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B110" s="3"/>
+      <c r="C110" s="3"/>
+    </row>
+    <row r="111" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B111" s="3"/>
+      <c r="C111" s="3"/>
+    </row>
+    <row r="112" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B112" s="3"/>
+      <c r="C112" s="3"/>
+    </row>
+    <row r="113" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B113" s="3"/>
+      <c r="C113" s="3"/>
+    </row>
+    <row r="114" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B114" s="3"/>
+      <c r="C114" s="3"/>
+    </row>
+    <row r="115" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
+    </row>
+    <row r="116" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B116" s="3"/>
+      <c r="C116" s="3"/>
+    </row>
+    <row r="117" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B117" s="3"/>
+      <c r="C117" s="3"/>
+    </row>
+    <row r="118" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B118" s="3"/>
+      <c r="C118" s="3"/>
+    </row>
+    <row r="119" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B119" s="3"/>
+      <c r="C119" s="3"/>
+    </row>
+    <row r="120" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B120" s="3"/>
+      <c r="C120" s="3"/>
+    </row>
+    <row r="121" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B121" s="3"/>
+      <c r="C121" s="3"/>
+    </row>
+    <row r="122" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B122" s="3"/>
+      <c r="C122" s="3"/>
+    </row>
+    <row r="123" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B123" s="3"/>
+      <c r="C123" s="3"/>
+    </row>
+    <row r="124" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B124" s="3"/>
+      <c r="C124" s="3"/>
+    </row>
+    <row r="125" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B125" s="3"/>
+      <c r="C125" s="3"/>
+    </row>
+    <row r="126" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B126" s="3"/>
+      <c r="C126" s="3"/>
+    </row>
+    <row r="127" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B127" s="3"/>
+      <c r="C127" s="3"/>
+    </row>
+    <row r="128" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B128" s="3"/>
+      <c r="C128" s="3"/>
+    </row>
+    <row r="129" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B129" s="3"/>
+      <c r="C129" s="3"/>
+    </row>
+    <row r="130" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B130" s="3"/>
+      <c r="C130" s="3"/>
+    </row>
+    <row r="131" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B131" s="3"/>
+      <c r="C131" s="3"/>
+    </row>
+    <row r="132" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B132" s="3"/>
+      <c r="C132" s="3"/>
+    </row>
+    <row r="133" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B133" s="3"/>
+      <c r="C133" s="3"/>
+    </row>
+    <row r="134" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B134" s="3"/>
+      <c r="C134" s="3"/>
+    </row>
+    <row r="135" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B135" s="3"/>
+      <c r="C135" s="3"/>
+    </row>
+    <row r="136" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B136" s="3"/>
+      <c r="C136" s="3"/>
+    </row>
+    <row r="137" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B137" s="3"/>
+      <c r="C137" s="3"/>
+    </row>
+    <row r="138" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B138" s="3"/>
+      <c r="C138" s="3"/>
+    </row>
+    <row r="139" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B139" s="3"/>
+      <c r="C139" s="3"/>
+    </row>
+    <row r="140" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B140" s="3"/>
+      <c r="C140" s="3"/>
+    </row>
+    <row r="141" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B141" s="3"/>
+      <c r="C141" s="3"/>
+    </row>
+    <row r="142" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B142" s="3"/>
+      <c r="C142" s="3"/>
+    </row>
+    <row r="143" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B143" s="3"/>
+      <c r="C143" s="3"/>
+    </row>
+    <row r="144" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B144" s="3"/>
+      <c r="C144" s="3"/>
+    </row>
+    <row r="145" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B145" s="3"/>
+      <c r="C145" s="3"/>
+    </row>
+    <row r="146" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B146" s="3"/>
+      <c r="C146" s="3"/>
+    </row>
+    <row r="147" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B147" s="3"/>
+      <c r="C147" s="3"/>
+    </row>
+    <row r="148" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B148" s="3"/>
+      <c r="C148" s="3"/>
+    </row>
+    <row r="149" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B149" s="3"/>
+      <c r="C149" s="3"/>
+    </row>
+    <row r="150" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B150" s="3"/>
+      <c r="C150" s="3"/>
+    </row>
+    <row r="151" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B151" s="3"/>
+      <c r="C151" s="3"/>
+    </row>
+    <row r="152" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B152" s="3"/>
+      <c r="C152" s="3"/>
+    </row>
+    <row r="153" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B153" s="3"/>
+      <c r="C153" s="3"/>
+    </row>
+    <row r="154" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B154" s="3"/>
+      <c r="C154" s="3"/>
+    </row>
+    <row r="155" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B155" s="3"/>
+      <c r="C155" s="3"/>
+    </row>
+    <row r="156" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B156" s="3"/>
+      <c r="C156" s="3"/>
+    </row>
+    <row r="157" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B157" s="3"/>
+      <c r="C157" s="3"/>
+    </row>
+    <row r="158" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B158" s="3"/>
+      <c r="C158" s="3"/>
+    </row>
+    <row r="159" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B159" s="3"/>
+      <c r="C159" s="3"/>
+    </row>
+    <row r="160" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B160" s="3"/>
+      <c r="C160" s="3"/>
+    </row>
+    <row r="161" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B161" s="3"/>
+      <c r="C161" s="3"/>
+    </row>
+    <row r="162" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B162" s="3"/>
+      <c r="C162" s="3"/>
+    </row>
+    <row r="163" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B163" s="3"/>
+      <c r="C163" s="3"/>
+    </row>
+    <row r="164" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B164" s="3"/>
+      <c r="C164" s="3"/>
+    </row>
+    <row r="165" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B165" s="3"/>
+      <c r="C165" s="3"/>
+    </row>
+    <row r="166" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B166" s="3"/>
+      <c r="C166" s="3"/>
+    </row>
+    <row r="167" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B167" s="3"/>
+      <c r="C167" s="3"/>
+    </row>
+    <row r="168" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B168" s="3"/>
+      <c r="C168" s="3"/>
+    </row>
+    <row r="169" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B169" s="3"/>
+      <c r="C169" s="3"/>
+    </row>
+    <row r="170" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B170" s="3"/>
+      <c r="C170" s="3"/>
+    </row>
+    <row r="171" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B171" s="3"/>
+      <c r="C171" s="3"/>
+    </row>
+    <row r="172" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B172" s="3"/>
+      <c r="C172" s="3"/>
+    </row>
+    <row r="173" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B173" s="3"/>
+      <c r="C173" s="3"/>
+    </row>
+    <row r="174" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B174" s="3"/>
+      <c r="C174" s="3"/>
+    </row>
+    <row r="175" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B175" s="3"/>
+      <c r="C175" s="3"/>
+    </row>
+    <row r="176" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B176" s="3"/>
+      <c r="C176" s="3"/>
+    </row>
+    <row r="177" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B177" s="3"/>
+      <c r="C177" s="3"/>
+    </row>
+    <row r="178" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B178" s="3"/>
+      <c r="C178" s="3"/>
+    </row>
+    <row r="179" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B179" s="3"/>
+      <c r="C179" s="3"/>
+    </row>
+    <row r="180" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B180" s="3"/>
+      <c r="C180" s="3"/>
+    </row>
+    <row r="181" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B181" s="3"/>
+      <c r="C181" s="3"/>
+    </row>
+    <row r="182" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B182" s="3"/>
+      <c r="C182" s="3"/>
+    </row>
+    <row r="183" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B183" s="3"/>
+      <c r="C183" s="3"/>
+    </row>
+    <row r="184" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B184" s="3"/>
+      <c r="C184" s="3"/>
+    </row>
+    <row r="185" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B185" s="3"/>
+      <c r="C185" s="3"/>
+    </row>
+    <row r="186" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B186" s="3"/>
+      <c r="C186" s="3"/>
+    </row>
+    <row r="187" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B187" s="3"/>
+      <c r="C187" s="3"/>
+    </row>
+    <row r="188" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B188" s="3"/>
+      <c r="C188" s="3"/>
+    </row>
+    <row r="189" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B189" s="3"/>
+      <c r="C189" s="3"/>
+    </row>
+    <row r="190" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B190" s="3"/>
+      <c r="C190" s="3"/>
+    </row>
+    <row r="191" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B191" s="3"/>
+      <c r="C191" s="3"/>
+    </row>
+    <row r="192" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B192" s="3"/>
+      <c r="C192" s="3"/>
+    </row>
+    <row r="193" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B193" s="3"/>
+      <c r="C193" s="3"/>
+    </row>
+    <row r="194" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B194" s="3"/>
+      <c r="C194" s="3"/>
+    </row>
+    <row r="195" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B195" s="3"/>
+      <c r="C195" s="3"/>
+    </row>
+    <row r="196" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B196" s="3"/>
+      <c r="C196" s="3"/>
+    </row>
+    <row r="197" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B197" s="3"/>
+      <c r="C197" s="3"/>
+    </row>
+    <row r="198" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B198" s="3"/>
+      <c r="C198" s="3"/>
+    </row>
+    <row r="199" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B199" s="3"/>
+      <c r="C199" s="3"/>
+    </row>
+    <row r="200" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B200" s="3"/>
+      <c r="C200" s="3"/>
+    </row>
+    <row r="201" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B201" s="3"/>
+      <c r="C201" s="3"/>
+    </row>
+    <row r="202" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B202" s="3"/>
+      <c r="C202" s="3"/>
+    </row>
+    <row r="203" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B203" s="3"/>
+      <c r="C203" s="3"/>
+    </row>
+    <row r="204" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B204" s="3"/>
+      <c r="C204" s="3"/>
+    </row>
+    <row r="205" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B205" s="3"/>
+      <c r="C205" s="3"/>
+    </row>
+    <row r="206" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B206" s="3"/>
+      <c r="C206" s="3"/>
+    </row>
+    <row r="207" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B207" s="3"/>
+      <c r="C207" s="3"/>
+    </row>
+    <row r="208" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B208" s="3"/>
+      <c r="C208" s="3"/>
+    </row>
+    <row r="209" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B209" s="3"/>
+      <c r="C209" s="3"/>
+    </row>
+    <row r="210" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B210" s="3"/>
+      <c r="C210" s="3"/>
+    </row>
+    <row r="211" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B211" s="3"/>
+      <c r="C211" s="3"/>
+    </row>
+    <row r="212" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B212" s="3"/>
+      <c r="C212" s="3"/>
+    </row>
+    <row r="213" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B213" s="3"/>
+      <c r="C213" s="3"/>
+    </row>
+    <row r="214" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B214" s="3"/>
+      <c r="C214" s="3"/>
+    </row>
+    <row r="215" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B215" s="3"/>
+      <c r="C215" s="3"/>
+    </row>
+    <row r="216" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B216" s="3"/>
+      <c r="C216" s="3"/>
+    </row>
+    <row r="217" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B217" s="3"/>
+      <c r="C217" s="3"/>
+    </row>
+    <row r="218" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B218" s="3"/>
+      <c r="C218" s="3"/>
+    </row>
+    <row r="219" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B219" s="3"/>
+      <c r="C219" s="3"/>
+    </row>
+    <row r="220" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B220" s="3"/>
+      <c r="C220" s="3"/>
+    </row>
+    <row r="221" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B221" s="3"/>
+      <c r="C221" s="3"/>
+    </row>
+    <row r="222" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B222" s="3"/>
+      <c r="C222" s="3"/>
+    </row>
+    <row r="223" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B223" s="3"/>
+      <c r="C223" s="3"/>
+    </row>
+    <row r="224" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B224" s="3"/>
+      <c r="C224" s="3"/>
+    </row>
+    <row r="225" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B225" s="3"/>
+      <c r="C225" s="3"/>
+    </row>
+    <row r="226" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B226" s="3"/>
+      <c r="C226" s="3"/>
+    </row>
+    <row r="227" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B227" s="3"/>
+      <c r="C227" s="3"/>
+    </row>
+    <row r="228" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B228" s="3"/>
+      <c r="C228" s="3"/>
+    </row>
+    <row r="229" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B229" s="3"/>
+      <c r="C229" s="3"/>
+    </row>
+    <row r="230" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B230" s="3"/>
+      <c r="C230" s="3"/>
+    </row>
+    <row r="231" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B231" s="3"/>
+      <c r="C231" s="3"/>
+    </row>
+    <row r="232" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B232" s="3"/>
+      <c r="C232" s="3"/>
+    </row>
+    <row r="233" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B233" s="3"/>
+      <c r="C233" s="3"/>
+    </row>
+    <row r="234" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B234" s="3"/>
+      <c r="C234" s="3"/>
+    </row>
+    <row r="235" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B235" s="3"/>
+      <c r="C235" s="3"/>
+    </row>
+    <row r="236" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B236" s="3"/>
+      <c r="C236" s="3"/>
+    </row>
+    <row r="237" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B237" s="3"/>
+      <c r="C237" s="3"/>
+    </row>
+    <row r="238" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B238" s="3"/>
+      <c r="C238" s="3"/>
+    </row>
+    <row r="239" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B239" s="3"/>
+      <c r="C239" s="3"/>
+    </row>
+    <row r="240" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B240" s="3"/>
+      <c r="C240" s="3"/>
+    </row>
+    <row r="241" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B241" s="3"/>
+      <c r="C241" s="3"/>
+    </row>
+    <row r="242" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B242" s="3"/>
+      <c r="C242" s="3"/>
+    </row>
+    <row r="243" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B243" s="3"/>
+      <c r="C243" s="3"/>
+    </row>
+    <row r="244" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B244" s="3"/>
+      <c r="C244" s="3"/>
+    </row>
+    <row r="245" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B245" s="3"/>
+      <c r="C245" s="3"/>
+    </row>
+    <row r="246" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B246" s="3"/>
+      <c r="C246" s="3"/>
+    </row>
+    <row r="247" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B247" s="3"/>
+      <c r="C247" s="3"/>
+    </row>
+    <row r="248" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B248" s="3"/>
+      <c r="C248" s="3"/>
+    </row>
+    <row r="249" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B249" s="3"/>
+      <c r="C249" s="3"/>
+    </row>
+    <row r="250" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B250" s="3"/>
+      <c r="C250" s="3"/>
+    </row>
+    <row r="251" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B251" s="3"/>
+      <c r="C251" s="3"/>
+    </row>
+    <row r="252" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B252" s="3"/>
+      <c r="C252" s="3"/>
+    </row>
+    <row r="253" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B253" s="3"/>
+      <c r="C253" s="3"/>
+    </row>
+    <row r="254" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B254" s="3"/>
+      <c r="C254" s="3"/>
+    </row>
+    <row r="255" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B255" s="3"/>
+      <c r="C255" s="3"/>
+    </row>
+    <row r="256" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B256" s="3"/>
+      <c r="C256" s="3"/>
+    </row>
+    <row r="257" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B257" s="3"/>
+      <c r="C257" s="3"/>
+    </row>
+    <row r="258" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B258" s="3"/>
+      <c r="C258" s="3"/>
+    </row>
+    <row r="259" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B259" s="3"/>
+      <c r="C259" s="3"/>
+    </row>
+    <row r="260" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B260" s="3"/>
+      <c r="C260" s="3"/>
+    </row>
+    <row r="261" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B261" s="3"/>
+      <c r="C261" s="3"/>
+    </row>
+    <row r="262" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B262" s="3"/>
+      <c r="C262" s="3"/>
+    </row>
+    <row r="263" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B263" s="3"/>
+      <c r="C263" s="3"/>
+    </row>
+    <row r="264" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B264" s="3"/>
+      <c r="C264" s="3"/>
+    </row>
+    <row r="265" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B265" s="3"/>
+      <c r="C265" s="3"/>
+    </row>
+    <row r="266" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B266" s="3"/>
+      <c r="C266" s="3"/>
+    </row>
+    <row r="267" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B267" s="3"/>
+      <c r="C267" s="3"/>
+    </row>
+    <row r="268" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B268" s="3"/>
+      <c r="C268" s="3"/>
+    </row>
+    <row r="269" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B269" s="3"/>
+      <c r="C269" s="3"/>
+    </row>
+    <row r="270" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B270" s="3"/>
+      <c r="C270" s="3"/>
+    </row>
+    <row r="271" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B271" s="3"/>
+      <c r="C271" s="3"/>
+    </row>
+    <row r="272" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B272" s="3"/>
+      <c r="C272" s="3"/>
+    </row>
+    <row r="273" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B273" s="3"/>
+      <c r="C273" s="3"/>
+    </row>
+    <row r="274" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B274" s="3"/>
+      <c r="C274" s="3"/>
+    </row>
+    <row r="275" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B275" s="3"/>
+      <c r="C275" s="3"/>
+    </row>
+    <row r="276" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B276" s="3"/>
+      <c r="C276" s="3"/>
+    </row>
+    <row r="277" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B277" s="3"/>
+      <c r="C277" s="3"/>
+    </row>
+    <row r="278" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B278" s="3"/>
+      <c r="C278" s="3"/>
+    </row>
+    <row r="279" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B279" s="3"/>
+      <c r="C279" s="3"/>
+    </row>
+    <row r="280" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B280" s="3"/>
+      <c r="C280" s="3"/>
+    </row>
+    <row r="281" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B281" s="3"/>
+      <c r="C281" s="3"/>
+    </row>
+    <row r="282" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B282" s="3"/>
+      <c r="C282" s="3"/>
+    </row>
+    <row r="283" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B283" s="3"/>
+      <c r="C283" s="3"/>
+    </row>
+    <row r="284" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B284" s="3"/>
+      <c r="C284" s="3"/>
+    </row>
+    <row r="285" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B285" s="3"/>
+      <c r="C285" s="3"/>
+    </row>
+    <row r="286" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B286" s="3"/>
+      <c r="C286" s="3"/>
+    </row>
+    <row r="287" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B287" s="3"/>
+      <c r="C287" s="3"/>
+    </row>
+    <row r="288" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B288" s="3"/>
+      <c r="C288" s="3"/>
+    </row>
+    <row r="289" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B289" s="3"/>
+      <c r="C289" s="3"/>
+    </row>
+    <row r="290" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B290" s="3"/>
+      <c r="C290" s="3"/>
+    </row>
+    <row r="291" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B291" s="3"/>
+      <c r="C291" s="3"/>
+    </row>
+    <row r="292" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B292" s="3"/>
+      <c r="C292" s="3"/>
+    </row>
+    <row r="293" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B293" s="3"/>
+      <c r="C293" s="3"/>
+    </row>
+    <row r="294" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B294" s="3"/>
+      <c r="C294" s="3"/>
+    </row>
+    <row r="295" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B295" s="3"/>
+      <c r="C295" s="3"/>
+    </row>
+    <row r="296" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B296" s="3"/>
+      <c r="C296" s="3"/>
+    </row>
+    <row r="297" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B297" s="3"/>
+      <c r="C297" s="3"/>
+    </row>
+    <row r="298" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B298" s="3"/>
+      <c r="C298" s="3"/>
+    </row>
+    <row r="299" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B299" s="3"/>
+      <c r="C299" s="3"/>
+    </row>
+    <row r="300" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B300" s="3"/>
+      <c r="C300" s="3"/>
+    </row>
+    <row r="301" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B301" s="3"/>
+      <c r="C301" s="3"/>
+    </row>
+    <row r="302" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B302" s="3"/>
+      <c r="C302" s="3"/>
+    </row>
+    <row r="303" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B303" s="3"/>
+      <c r="C303" s="3"/>
+    </row>
+    <row r="304" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B304" s="3"/>
+      <c r="C304" s="3"/>
+    </row>
+    <row r="305" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B305" s="3"/>
+      <c r="C305" s="3"/>
+    </row>
+    <row r="306" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B306" s="3"/>
+      <c r="C306" s="3"/>
+    </row>
+    <row r="307" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B307" s="3"/>
+      <c r="C307" s="3"/>
+    </row>
+    <row r="308" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B308" s="3"/>
+      <c r="C308" s="3"/>
+    </row>
+    <row r="309" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B309" s="3"/>
+      <c r="C309" s="3"/>
+    </row>
+    <row r="310" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B310" s="3"/>
+      <c r="C310" s="3"/>
+    </row>
+    <row r="311" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B311" s="3"/>
+      <c r="C311" s="3"/>
+    </row>
+    <row r="312" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B312" s="3"/>
+      <c r="C312" s="3"/>
+    </row>
+    <row r="313" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B313" s="3"/>
+      <c r="C313" s="3"/>
+    </row>
+    <row r="314" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B314" s="3"/>
+      <c r="C314" s="3"/>
+    </row>
+    <row r="315" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B315" s="3"/>
+      <c r="C315" s="3"/>
+    </row>
+    <row r="316" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B316" s="3"/>
+      <c r="C316" s="3"/>
+    </row>
+    <row r="317" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B317" s="3"/>
+      <c r="C317" s="3"/>
+    </row>
+    <row r="318" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B318" s="3"/>
+      <c r="C318" s="3"/>
+    </row>
+    <row r="319" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B319" s="3"/>
+      <c r="C319" s="3"/>
+    </row>
+    <row r="320" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B320" s="3"/>
+      <c r="C320" s="3"/>
+    </row>
+    <row r="321" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B321" s="3"/>
+      <c r="C321" s="3"/>
+    </row>
+    <row r="322" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B322" s="3"/>
+      <c r="C322" s="3"/>
+    </row>
+    <row r="323" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B323" s="3"/>
+      <c r="C323" s="3"/>
+    </row>
+    <row r="324" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B324" s="3"/>
+      <c r="C324" s="3"/>
+    </row>
+    <row r="325" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B325" s="3"/>
+      <c r="C325" s="3"/>
+    </row>
+    <row r="326" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B326" s="3"/>
+      <c r="C326" s="3"/>
+    </row>
+    <row r="327" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B327" s="3"/>
+      <c r="C327" s="3"/>
+    </row>
+    <row r="328" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B328" s="3"/>
+      <c r="C328" s="3"/>
+    </row>
+    <row r="329" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B329" s="3"/>
+      <c r="C329" s="3"/>
+    </row>
+    <row r="330" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B330" s="3"/>
+      <c r="C330" s="3"/>
+    </row>
+    <row r="331" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B331" s="3"/>
+      <c r="C331" s="3"/>
+    </row>
+    <row r="332" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B332" s="3"/>
+      <c r="C332" s="3"/>
+    </row>
+    <row r="333" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B333" s="3"/>
+      <c r="C333" s="3"/>
+    </row>
+    <row r="334" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B334" s="3"/>
+      <c r="C334" s="3"/>
+    </row>
+    <row r="335" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B335" s="3"/>
+      <c r="C335" s="3"/>
+    </row>
+    <row r="336" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B336" s="3"/>
+      <c r="C336" s="3"/>
+    </row>
+    <row r="337" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B337" s="3"/>
+      <c r="C337" s="3"/>
+    </row>
+    <row r="338" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B338" s="3"/>
+      <c r="C338" s="3"/>
+    </row>
+    <row r="339" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B339" s="3"/>
+      <c r="C339" s="3"/>
+    </row>
+    <row r="340" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B340" s="3"/>
+      <c r="C340" s="3"/>
+    </row>
+    <row r="341" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B341" s="3"/>
+      <c r="C341" s="3"/>
+    </row>
+    <row r="342" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B342" s="3"/>
+      <c r="C342" s="3"/>
+    </row>
+    <row r="343" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B343" s="3"/>
+      <c r="C343" s="3"/>
+    </row>
+    <row r="344" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B344" s="3"/>
+      <c r="C344" s="3"/>
+    </row>
+    <row r="345" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B345" s="3"/>
+      <c r="C345" s="3"/>
+    </row>
+    <row r="346" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B346" s="3"/>
+      <c r="C346" s="3"/>
+    </row>
+    <row r="347" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B347" s="3"/>
+      <c r="C347" s="3"/>
+    </row>
+    <row r="348" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B348" s="3"/>
+      <c r="C348" s="3"/>
+    </row>
+    <row r="349" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B349" s="3"/>
+      <c r="C349" s="3"/>
+    </row>
+    <row r="350" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B350" s="3"/>
+      <c r="C350" s="3"/>
+    </row>
+    <row r="351" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B351" s="3"/>
+      <c r="C351" s="3"/>
+    </row>
+    <row r="352" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B352" s="3"/>
+      <c r="C352" s="3"/>
+    </row>
+    <row r="353" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B353" s="3"/>
+      <c r="C353" s="3"/>
+    </row>
+    <row r="354" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B354" s="3"/>
+      <c r="C354" s="3"/>
+    </row>
+    <row r="355" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B355" s="3"/>
+      <c r="C355" s="3"/>
+    </row>
+    <row r="356" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B356" s="3"/>
+      <c r="C356" s="3"/>
+    </row>
+    <row r="357" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B357" s="3"/>
+      <c r="C357" s="3"/>
+    </row>
+    <row r="358" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B358" s="3"/>
+      <c r="C358" s="3"/>
+    </row>
+    <row r="359" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B359" s="3"/>
+      <c r="C359" s="3"/>
+    </row>
+    <row r="360" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B360" s="3"/>
+      <c r="C360" s="3"/>
+    </row>
+    <row r="361" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B361" s="3"/>
+      <c r="C361" s="3"/>
+    </row>
+    <row r="362" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B362" s="3"/>
+      <c r="C362" s="3"/>
+    </row>
+    <row r="363" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B363" s="3"/>
+      <c r="C363" s="3"/>
+    </row>
+    <row r="364" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B364" s="3"/>
+      <c r="C364" s="3"/>
+    </row>
+    <row r="365" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B365" s="3"/>
+      <c r="C365" s="3"/>
+    </row>
+    <row r="366" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B366" s="3"/>
+      <c r="C366" s="3"/>
+    </row>
+    <row r="367" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B367" s="3"/>
+      <c r="C367" s="3"/>
+    </row>
+    <row r="368" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B368" s="3"/>
+      <c r="C368" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Unknown SensorType" error="Please define a SensorType in the Tab SensorType before adding it as a Sensor here." xr:uid="{523F0DEC-D848-9F41-8BE7-A04F215375F8}">
+          <x14:formula1>
+            <xm:f>SensorTypes!$A:$A</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B368</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Unknown Platform" xr:uid="{47905CD5-888B-BA46-B2EE-CF9B965604C4}">
+          <x14:formula1>
+            <xm:f>Platforms!$A:$A</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:C368</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.109375" customWidth="1"/>
+    <col min="1" max="1" width="30.1640625" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" customWidth="1"/>
-    <col min="3" max="3" width="20.44140625" customWidth="1"/>
+    <col min="3" max="3" width="20.5" customWidth="1"/>
     <col min="4" max="4" width="60.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>6</v>
       </c>
+      <c r="D1" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="3"/>
+      <c r="D2" s="9"/>
+    </row>
+    <row r="3" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="3"/>
+    </row>
+    <row r="4" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Only TRUE/FALSE allowed" sqref="C2:C522" xr:uid="{FB859064-8F6E-4A4C-A52A-079A22CB8A40}">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="UnknownSensorType" error="Please define the SensorType before using it here." xr:uid="{CA481EEE-5A17-AD4E-8C05-050A00DF7727}">
+          <x14:formula1>
+            <xm:f>SensorTypes!$A:$A</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B378</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
+  <dimension ref="A1:F668"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>178</v>
+      </c>
       <c r="C1" s="4" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B2" s="3"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B3" s="3"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B4" s="3"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B5" s="3"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B6" s="3"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B8" s="3"/>
     </row>
-    <row r="9" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B9" s="3"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B10" s="3"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B11" s="3"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B12" s="3"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B13" s="3"/>
     </row>
-    <row r="14" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B14" s="3"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B15" s="3"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B16" s="3"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B17" s="3"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B18" s="3"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B19" s="3"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B20" s="3"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B21" s="3"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B22" s="3"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B23" s="3"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B24" s="3"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B25" s="3"/>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B26" s="3"/>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B27" s="3"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="4"/>
+      <c r="B28" s="3"/>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B29" s="3"/>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B30" s="3"/>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B31" s="3"/>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B32" s="3"/>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B33" s="3"/>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B34" s="3"/>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B35" s="3"/>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B36" s="3"/>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B37" s="3"/>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B38" s="3"/>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B39" s="3"/>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B40" s="3"/>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B41" s="3"/>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B42" s="3"/>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B43" s="3"/>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B44" s="3"/>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B45" s="3"/>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B46" s="3"/>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B47" s="3"/>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B48" s="3"/>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B49" s="3"/>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B50" s="3"/>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B51" s="3"/>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B52" s="3"/>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B53" s="3"/>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B54" s="3"/>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B55" s="3"/>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B56" s="3"/>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B57" s="3"/>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B58" s="3"/>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B59" s="3"/>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B60" s="3"/>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B61" s="3"/>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B62" s="3"/>
+    </row>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B63" s="3"/>
+    </row>
+    <row r="64" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B64" s="3"/>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B65" s="3"/>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B66" s="3"/>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B67" s="3"/>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B68" s="3"/>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B69" s="3"/>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B70" s="3"/>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B71" s="3"/>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B72" s="3"/>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B73" s="3"/>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B74" s="3"/>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B75" s="3"/>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B76" s="3"/>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B77" s="3"/>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B78" s="3"/>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B79" s="3"/>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B80" s="3"/>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B81" s="3"/>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B82" s="3"/>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B83" s="3"/>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B84" s="3"/>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B85" s="3"/>
+    </row>
+    <row r="86" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B86" s="3"/>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B87" s="3"/>
+    </row>
+    <row r="88" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B88" s="3"/>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B89" s="3"/>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B90" s="3"/>
+    </row>
+    <row r="91" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B91" s="3"/>
+    </row>
+    <row r="92" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B92" s="3"/>
+    </row>
+    <row r="93" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B93" s="3"/>
+    </row>
+    <row r="94" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B94" s="3"/>
+    </row>
+    <row r="95" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B95" s="3"/>
+    </row>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B96" s="3"/>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B97" s="3"/>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B98" s="3"/>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B99" s="3"/>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B100" s="3"/>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B101" s="3"/>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B102" s="3"/>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B103" s="3"/>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B104" s="3"/>
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B105" s="3"/>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B106" s="3"/>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B107" s="3"/>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B108" s="3"/>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B109" s="3"/>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B110" s="3"/>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B111" s="3"/>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B112" s="3"/>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B113" s="3"/>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B114" s="3"/>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B115" s="3"/>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B116" s="3"/>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B117" s="3"/>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B118" s="3"/>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B119" s="3"/>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B120" s="3"/>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B121" s="3"/>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B122" s="3"/>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B123" s="3"/>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B124" s="3"/>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B125" s="3"/>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B126" s="3"/>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B127" s="3"/>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B128" s="3"/>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B129" s="3"/>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B130" s="3"/>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B131" s="3"/>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B132" s="3"/>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B133" s="3"/>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B134" s="3"/>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B135" s="3"/>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B136" s="3"/>
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B137" s="3"/>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B138" s="3"/>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B139" s="3"/>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B140" s="3"/>
+    </row>
+    <row r="141" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B141" s="3"/>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B142" s="3"/>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B143" s="3"/>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B144" s="3"/>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B145" s="3"/>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B146" s="3"/>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B147" s="3"/>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B148" s="3"/>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B149" s="3"/>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B150" s="3"/>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B151" s="3"/>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B152" s="3"/>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B153" s="3"/>
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B154" s="3"/>
+    </row>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B155" s="3"/>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B156" s="3"/>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B157" s="3"/>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B158" s="3"/>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B159" s="3"/>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B160" s="3"/>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B161" s="3"/>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B162" s="3"/>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B163" s="3"/>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B164" s="3"/>
+    </row>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B165" s="3"/>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B166" s="3"/>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B167" s="3"/>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B168" s="3"/>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B169" s="3"/>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B170" s="3"/>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B171" s="3"/>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B172" s="3"/>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B173" s="3"/>
+    </row>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B174" s="3"/>
+    </row>
+    <row r="175" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B175" s="3"/>
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B176" s="3"/>
+    </row>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B177" s="3"/>
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B178" s="3"/>
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B179" s="3"/>
+    </row>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B180" s="3"/>
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B181" s="3"/>
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B182" s="3"/>
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B183" s="3"/>
+    </row>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B184" s="3"/>
+    </row>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B185" s="3"/>
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B186" s="3"/>
+    </row>
+    <row r="187" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B187" s="3"/>
+    </row>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B188" s="3"/>
+    </row>
+    <row r="189" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B189" s="3"/>
+    </row>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B190" s="3"/>
+    </row>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B191" s="3"/>
+    </row>
+    <row r="192" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B192" s="3"/>
+    </row>
+    <row r="193" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B193" s="3"/>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B194" s="3"/>
+    </row>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B195" s="3"/>
+    </row>
+    <row r="196" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B196" s="3"/>
+    </row>
+    <row r="197" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B197" s="3"/>
+    </row>
+    <row r="198" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B198" s="3"/>
+    </row>
+    <row r="199" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B199" s="3"/>
+    </row>
+    <row r="200" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B200" s="3"/>
+    </row>
+    <row r="201" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B201" s="3"/>
+    </row>
+    <row r="202" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B202" s="3"/>
+    </row>
+    <row r="203" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B203" s="3"/>
+    </row>
+    <row r="204" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B204" s="3"/>
+    </row>
+    <row r="205" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B205" s="3"/>
+    </row>
+    <row r="206" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B206" s="3"/>
+    </row>
+    <row r="207" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B207" s="3"/>
+    </row>
+    <row r="208" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B208" s="3"/>
+    </row>
+    <row r="209" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B209" s="3"/>
+    </row>
+    <row r="210" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B210" s="3"/>
+    </row>
+    <row r="211" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B211" s="3"/>
+    </row>
+    <row r="212" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B212" s="3"/>
+    </row>
+    <row r="213" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B213" s="3"/>
+    </row>
+    <row r="214" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B214" s="3"/>
+    </row>
+    <row r="215" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B215" s="3"/>
+    </row>
+    <row r="216" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B216" s="3"/>
+    </row>
+    <row r="217" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B217" s="3"/>
+    </row>
+    <row r="218" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B218" s="3"/>
+    </row>
+    <row r="219" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B219" s="3"/>
+    </row>
+    <row r="220" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B220" s="3"/>
+    </row>
+    <row r="221" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B221" s="3"/>
+    </row>
+    <row r="222" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B222" s="3"/>
+    </row>
+    <row r="223" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B223" s="3"/>
+    </row>
+    <row r="224" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B224" s="3"/>
+    </row>
+    <row r="225" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B225" s="3"/>
+    </row>
+    <row r="226" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B226" s="3"/>
+    </row>
+    <row r="227" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B227" s="3"/>
+    </row>
+    <row r="228" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B228" s="3"/>
+    </row>
+    <row r="229" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B229" s="3"/>
+    </row>
+    <row r="230" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B230" s="3"/>
+    </row>
+    <row r="231" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B231" s="3"/>
+    </row>
+    <row r="232" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B232" s="3"/>
+    </row>
+    <row r="233" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B233" s="3"/>
+    </row>
+    <row r="234" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B234" s="3"/>
+    </row>
+    <row r="235" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B235" s="3"/>
+    </row>
+    <row r="236" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B236" s="3"/>
+    </row>
+    <row r="237" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B237" s="3"/>
+    </row>
+    <row r="238" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B238" s="3"/>
+    </row>
+    <row r="239" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B239" s="3"/>
+    </row>
+    <row r="240" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B240" s="3"/>
+    </row>
+    <row r="241" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B241" s="3"/>
+    </row>
+    <row r="242" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B242" s="3"/>
+    </row>
+    <row r="243" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B243" s="3"/>
+    </row>
+    <row r="244" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B244" s="3"/>
+    </row>
+    <row r="245" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B245" s="3"/>
+    </row>
+    <row r="246" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B246" s="3"/>
+    </row>
+    <row r="247" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B247" s="3"/>
+    </row>
+    <row r="248" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B248" s="3"/>
+    </row>
+    <row r="249" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B249" s="3"/>
+    </row>
+    <row r="250" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B250" s="3"/>
+    </row>
+    <row r="251" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B251" s="3"/>
+    </row>
+    <row r="252" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B252" s="3"/>
+    </row>
+    <row r="253" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B253" s="3"/>
+    </row>
+    <row r="254" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B254" s="3"/>
+    </row>
+    <row r="255" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B255" s="3"/>
+    </row>
+    <row r="256" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B256" s="3"/>
+    </row>
+    <row r="257" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B257" s="3"/>
+    </row>
+    <row r="258" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B258" s="3"/>
+    </row>
+    <row r="259" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B259" s="3"/>
+    </row>
+    <row r="260" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B260" s="3"/>
+    </row>
+    <row r="261" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B261" s="3"/>
+    </row>
+    <row r="262" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B262" s="3"/>
+    </row>
+    <row r="263" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B263" s="3"/>
+    </row>
+    <row r="264" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B264" s="3"/>
+    </row>
+    <row r="265" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B265" s="3"/>
+    </row>
+    <row r="266" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B266" s="3"/>
+    </row>
+    <row r="267" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B267" s="3"/>
+    </row>
+    <row r="268" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B268" s="3"/>
+    </row>
+    <row r="269" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B269" s="3"/>
+    </row>
+    <row r="270" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B270" s="3"/>
+    </row>
+    <row r="271" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B271" s="3"/>
+    </row>
+    <row r="272" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B272" s="3"/>
+    </row>
+    <row r="273" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B273" s="3"/>
+    </row>
+    <row r="274" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B274" s="3"/>
+    </row>
+    <row r="275" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B275" s="3"/>
+    </row>
+    <row r="276" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B276" s="3"/>
+    </row>
+    <row r="277" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B277" s="3"/>
+    </row>
+    <row r="278" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B278" s="3"/>
+    </row>
+    <row r="279" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B279" s="3"/>
+    </row>
+    <row r="280" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B280" s="3"/>
+    </row>
+    <row r="281" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B281" s="3"/>
+    </row>
+    <row r="282" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B282" s="3"/>
+    </row>
+    <row r="283" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B283" s="3"/>
+    </row>
+    <row r="284" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B284" s="3"/>
+    </row>
+    <row r="285" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B285" s="3"/>
+    </row>
+    <row r="286" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B286" s="3"/>
+    </row>
+    <row r="287" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B287" s="3"/>
+    </row>
+    <row r="288" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B288" s="3"/>
+    </row>
+    <row r="289" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B289" s="3"/>
+    </row>
+    <row r="290" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B290" s="3"/>
+    </row>
+    <row r="291" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B291" s="3"/>
+    </row>
+    <row r="292" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B292" s="3"/>
+    </row>
+    <row r="293" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B293" s="3"/>
+    </row>
+    <row r="294" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B294" s="3"/>
+    </row>
+    <row r="295" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B295" s="3"/>
+    </row>
+    <row r="296" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B296" s="3"/>
+    </row>
+    <row r="297" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B297" s="3"/>
+    </row>
+    <row r="298" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B298" s="3"/>
+    </row>
+    <row r="299" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B299" s="3"/>
+    </row>
+    <row r="300" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B300" s="3"/>
+    </row>
+    <row r="301" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B301" s="3"/>
+    </row>
+    <row r="302" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B302" s="3"/>
+    </row>
+    <row r="303" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B303" s="3"/>
+    </row>
+    <row r="304" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B304" s="3"/>
+    </row>
+    <row r="305" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B305" s="3"/>
+    </row>
+    <row r="306" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B306" s="3"/>
+    </row>
+    <row r="307" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B307" s="3"/>
+    </row>
+    <row r="308" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B308" s="3"/>
+    </row>
+    <row r="309" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B309" s="3"/>
+    </row>
+    <row r="310" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B310" s="3"/>
+    </row>
+    <row r="311" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B311" s="3"/>
+    </row>
+    <row r="312" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B312" s="3"/>
+    </row>
+    <row r="313" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B313" s="3"/>
+    </row>
+    <row r="314" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B314" s="3"/>
+    </row>
+    <row r="315" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B315" s="3"/>
+    </row>
+    <row r="316" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B316" s="3"/>
+    </row>
+    <row r="317" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B317" s="3"/>
+    </row>
+    <row r="318" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B318" s="3"/>
+    </row>
+    <row r="319" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B319" s="3"/>
+    </row>
+    <row r="320" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B320" s="3"/>
+    </row>
+    <row r="321" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B321" s="3"/>
+    </row>
+    <row r="322" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B322" s="3"/>
+    </row>
+    <row r="323" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B323" s="3"/>
+    </row>
+    <row r="324" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B324" s="3"/>
+    </row>
+    <row r="325" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B325" s="3"/>
+    </row>
+    <row r="326" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B326" s="3"/>
+    </row>
+    <row r="327" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B327" s="3"/>
+    </row>
+    <row r="328" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B328" s="3"/>
+    </row>
+    <row r="329" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B329" s="3"/>
+    </row>
+    <row r="330" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B330" s="3"/>
+    </row>
+    <row r="331" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B331" s="3"/>
+    </row>
+    <row r="332" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B332" s="3"/>
+    </row>
+    <row r="333" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B333" s="3"/>
+    </row>
+    <row r="334" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B334" s="3"/>
+    </row>
+    <row r="335" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B335" s="3"/>
+    </row>
+    <row r="336" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B336" s="3"/>
+    </row>
+    <row r="337" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B337" s="3"/>
+    </row>
+    <row r="338" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B338" s="3"/>
+    </row>
+    <row r="339" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B339" s="3"/>
+    </row>
+    <row r="340" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B340" s="3"/>
+    </row>
+    <row r="341" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B341" s="3"/>
+    </row>
+    <row r="342" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B342" s="3"/>
+    </row>
+    <row r="343" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B343" s="3"/>
+    </row>
+    <row r="344" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B344" s="3"/>
+    </row>
+    <row r="345" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B345" s="3"/>
+    </row>
+    <row r="346" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B346" s="3"/>
+    </row>
+    <row r="347" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B347" s="3"/>
+    </row>
+    <row r="348" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B348" s="3"/>
+    </row>
+    <row r="349" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B349" s="3"/>
+    </row>
+    <row r="350" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B350" s="3"/>
+    </row>
+    <row r="351" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B351" s="3"/>
+    </row>
+    <row r="352" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B352" s="3"/>
+    </row>
+    <row r="353" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B353" s="3"/>
+    </row>
+    <row r="354" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B354" s="3"/>
+    </row>
+    <row r="355" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B355" s="3"/>
+    </row>
+    <row r="356" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B356" s="3"/>
+    </row>
+    <row r="357" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B357" s="3"/>
+    </row>
+    <row r="358" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B358" s="3"/>
+    </row>
+    <row r="359" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B359" s="3"/>
+    </row>
+    <row r="360" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B360" s="3"/>
+    </row>
+    <row r="361" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B361" s="3"/>
+    </row>
+    <row r="362" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B362" s="3"/>
+    </row>
+    <row r="363" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B363" s="3"/>
+    </row>
+    <row r="364" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B364" s="3"/>
+    </row>
+    <row r="365" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B365" s="3"/>
+    </row>
+    <row r="366" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B366" s="3"/>
+    </row>
+    <row r="367" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B367" s="3"/>
+    </row>
+    <row r="368" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B368" s="3"/>
+    </row>
+    <row r="369" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B369" s="3"/>
+    </row>
+    <row r="370" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B370" s="3"/>
+    </row>
+    <row r="371" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B371" s="3"/>
+    </row>
+    <row r="372" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B372" s="3"/>
+    </row>
+    <row r="373" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B373" s="3"/>
+    </row>
+    <row r="374" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B374" s="3"/>
+    </row>
+    <row r="375" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B375" s="3"/>
+    </row>
+    <row r="376" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B376" s="3"/>
+    </row>
+    <row r="377" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B377" s="3"/>
+    </row>
+    <row r="378" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B378" s="3"/>
+    </row>
+    <row r="379" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B379" s="3"/>
+    </row>
+    <row r="380" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B380" s="3"/>
+    </row>
+    <row r="381" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B381" s="3"/>
+    </row>
+    <row r="382" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B382" s="3"/>
+    </row>
+    <row r="383" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B383" s="3"/>
+    </row>
+    <row r="384" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B384" s="3"/>
+    </row>
+    <row r="385" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B385" s="3"/>
+    </row>
+    <row r="386" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B386" s="3"/>
+    </row>
+    <row r="387" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B387" s="3"/>
+    </row>
+    <row r="388" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B388" s="3"/>
+    </row>
+    <row r="389" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B389" s="3"/>
+    </row>
+    <row r="390" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B390" s="3"/>
+    </row>
+    <row r="391" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B391" s="3"/>
+    </row>
+    <row r="392" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B392" s="3"/>
+    </row>
+    <row r="393" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B393" s="3"/>
+    </row>
+    <row r="394" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B394" s="3"/>
+    </row>
+    <row r="395" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B395" s="3"/>
+    </row>
+    <row r="396" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B396" s="3"/>
+    </row>
+    <row r="397" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B397" s="3"/>
+    </row>
+    <row r="398" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B398" s="3"/>
+    </row>
+    <row r="399" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B399" s="3"/>
+    </row>
+    <row r="400" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B400" s="3"/>
+    </row>
+    <row r="401" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B401" s="3"/>
+    </row>
+    <row r="402" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B402" s="3"/>
+    </row>
+    <row r="403" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B403" s="3"/>
+    </row>
+    <row r="404" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B404" s="3"/>
+    </row>
+    <row r="405" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B405" s="3"/>
+    </row>
+    <row r="406" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B406" s="3"/>
+    </row>
+    <row r="407" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B407" s="3"/>
+    </row>
+    <row r="408" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B408" s="3"/>
+    </row>
+    <row r="409" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B409" s="3"/>
+    </row>
+    <row r="410" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B410" s="3"/>
+    </row>
+    <row r="411" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B411" s="3"/>
+    </row>
+    <row r="412" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B412" s="3"/>
+    </row>
+    <row r="413" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B413" s="3"/>
+    </row>
+    <row r="414" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B414" s="3"/>
+    </row>
+    <row r="415" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B415" s="3"/>
+    </row>
+    <row r="416" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B416" s="3"/>
+    </row>
+    <row r="417" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B417" s="3"/>
+    </row>
+    <row r="418" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B418" s="3"/>
+    </row>
+    <row r="419" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B419" s="3"/>
+    </row>
+    <row r="420" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B420" s="3"/>
+    </row>
+    <row r="421" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B421" s="3"/>
+    </row>
+    <row r="422" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B422" s="3"/>
+    </row>
+    <row r="423" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B423" s="3"/>
+    </row>
+    <row r="424" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B424" s="3"/>
+    </row>
+    <row r="425" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B425" s="3"/>
+    </row>
+    <row r="426" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B426" s="3"/>
+    </row>
+    <row r="427" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B427" s="3"/>
+    </row>
+    <row r="428" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B428" s="3"/>
+    </row>
+    <row r="429" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B429" s="3"/>
+    </row>
+    <row r="430" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B430" s="3"/>
+    </row>
+    <row r="431" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B431" s="3"/>
+    </row>
+    <row r="432" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B432" s="3"/>
+    </row>
+    <row r="433" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B433" s="3"/>
+    </row>
+    <row r="434" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B434" s="3"/>
+    </row>
+    <row r="435" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B435" s="3"/>
+    </row>
+    <row r="436" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B436" s="3"/>
+    </row>
+    <row r="437" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B437" s="3"/>
+    </row>
+    <row r="438" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B438" s="3"/>
+    </row>
+    <row r="439" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B439" s="3"/>
+    </row>
+    <row r="440" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B440" s="3"/>
+    </row>
+    <row r="441" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B441" s="3"/>
+    </row>
+    <row r="442" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B442" s="3"/>
+    </row>
+    <row r="443" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B443" s="3"/>
+    </row>
+    <row r="444" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B444" s="3"/>
+    </row>
+    <row r="445" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B445" s="3"/>
+    </row>
+    <row r="446" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B446" s="3"/>
+    </row>
+    <row r="447" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B447" s="3"/>
+    </row>
+    <row r="448" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B448" s="3"/>
+    </row>
+    <row r="449" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B449" s="3"/>
+    </row>
+    <row r="450" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B450" s="3"/>
+    </row>
+    <row r="451" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B451" s="3"/>
+    </row>
+    <row r="452" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B452" s="3"/>
+    </row>
+    <row r="453" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B453" s="3"/>
+    </row>
+    <row r="454" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B454" s="3"/>
+    </row>
+    <row r="455" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B455" s="3"/>
+    </row>
+    <row r="456" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B456" s="3"/>
+    </row>
+    <row r="457" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B457" s="3"/>
+    </row>
+    <row r="458" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B458" s="3"/>
+    </row>
+    <row r="459" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B459" s="3"/>
+    </row>
+    <row r="460" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B460" s="3"/>
+    </row>
+    <row r="461" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B461" s="3"/>
+    </row>
+    <row r="462" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B462" s="3"/>
+    </row>
+    <row r="463" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B463" s="3"/>
+    </row>
+    <row r="464" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B464" s="3"/>
+    </row>
+    <row r="465" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B465" s="3"/>
+    </row>
+    <row r="466" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B466" s="3"/>
+    </row>
+    <row r="467" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B467" s="3"/>
+    </row>
+    <row r="468" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B468" s="3"/>
+    </row>
+    <row r="469" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B469" s="3"/>
+    </row>
+    <row r="470" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B470" s="3"/>
+    </row>
+    <row r="471" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B471" s="3"/>
+    </row>
+    <row r="472" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B472" s="3"/>
+    </row>
+    <row r="473" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B473" s="3"/>
+    </row>
+    <row r="474" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B474" s="3"/>
+    </row>
+    <row r="475" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B475" s="3"/>
+    </row>
+    <row r="476" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B476" s="3"/>
+    </row>
+    <row r="477" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B477" s="3"/>
+    </row>
+    <row r="478" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B478" s="3"/>
+    </row>
+    <row r="479" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B479" s="3"/>
+    </row>
+    <row r="480" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B480" s="3"/>
+    </row>
+    <row r="481" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B481" s="3"/>
+    </row>
+    <row r="482" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B482" s="3"/>
+    </row>
+    <row r="483" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B483" s="3"/>
+    </row>
+    <row r="484" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B484" s="3"/>
+    </row>
+    <row r="485" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B485" s="3"/>
+    </row>
+    <row r="486" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B486" s="3"/>
+    </row>
+    <row r="487" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B487" s="3"/>
+    </row>
+    <row r="488" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B488" s="3"/>
+    </row>
+    <row r="489" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B489" s="3"/>
+    </row>
+    <row r="490" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B490" s="3"/>
+    </row>
+    <row r="491" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B491" s="3"/>
+    </row>
+    <row r="492" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B492" s="3"/>
+    </row>
+    <row r="493" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B493" s="3"/>
+    </row>
+    <row r="494" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B494" s="3"/>
+    </row>
+    <row r="495" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B495" s="3"/>
+    </row>
+    <row r="496" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B496" s="3"/>
+    </row>
+    <row r="497" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B497" s="3"/>
+    </row>
+    <row r="498" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B498" s="3"/>
+    </row>
+    <row r="499" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B499" s="3"/>
+    </row>
+    <row r="500" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B500" s="3"/>
+    </row>
+    <row r="501" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B501" s="3"/>
+    </row>
+    <row r="502" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B502" s="3"/>
+    </row>
+    <row r="503" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B503" s="3"/>
+    </row>
+    <row r="504" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B504" s="3"/>
+    </row>
+    <row r="505" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B505" s="3"/>
+    </row>
+    <row r="506" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B506" s="3"/>
+    </row>
+    <row r="507" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B507" s="3"/>
+    </row>
+    <row r="508" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B508" s="3"/>
+    </row>
+    <row r="509" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B509" s="3"/>
+    </row>
+    <row r="510" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B510" s="3"/>
+    </row>
+    <row r="511" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B511" s="3"/>
+    </row>
+    <row r="512" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B512" s="3"/>
+    </row>
+    <row r="513" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B513" s="3"/>
+    </row>
+    <row r="514" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B514" s="3"/>
+    </row>
+    <row r="515" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B515" s="3"/>
+    </row>
+    <row r="516" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B516" s="3"/>
+    </row>
+    <row r="517" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B517" s="3"/>
+    </row>
+    <row r="518" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B518" s="3"/>
+    </row>
+    <row r="519" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B519" s="3"/>
+    </row>
+    <row r="520" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B520" s="3"/>
+    </row>
+    <row r="521" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B521" s="3"/>
+    </row>
+    <row r="522" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B522" s="3"/>
+    </row>
+    <row r="523" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B523" s="3"/>
+    </row>
+    <row r="524" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B524" s="3"/>
+    </row>
+    <row r="525" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B525" s="3"/>
+    </row>
+    <row r="526" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B526" s="3"/>
+    </row>
+    <row r="527" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B527" s="3"/>
+    </row>
+    <row r="528" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B528" s="3"/>
+    </row>
+    <row r="529" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B529" s="3"/>
+    </row>
+    <row r="530" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B530" s="3"/>
+    </row>
+    <row r="531" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B531" s="3"/>
+    </row>
+    <row r="532" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B532" s="3"/>
+    </row>
+    <row r="533" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B533" s="3"/>
+    </row>
+    <row r="534" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B534" s="3"/>
+    </row>
+    <row r="535" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B535" s="3"/>
+    </row>
+    <row r="536" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B536" s="3"/>
+    </row>
+    <row r="537" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B537" s="3"/>
+    </row>
+    <row r="538" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B538" s="3"/>
+    </row>
+    <row r="539" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B539" s="3"/>
+    </row>
+    <row r="540" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B540" s="3"/>
+    </row>
+    <row r="541" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B541" s="3"/>
+    </row>
+    <row r="542" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B542" s="3"/>
+    </row>
+    <row r="543" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B543" s="3"/>
+    </row>
+    <row r="544" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B544" s="3"/>
+    </row>
+    <row r="545" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B545" s="3"/>
+    </row>
+    <row r="546" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B546" s="3"/>
+    </row>
+    <row r="547" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B547" s="3"/>
+    </row>
+    <row r="548" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B548" s="3"/>
+    </row>
+    <row r="549" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B549" s="3"/>
+    </row>
+    <row r="550" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B550" s="3"/>
+    </row>
+    <row r="551" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B551" s="3"/>
+    </row>
+    <row r="552" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B552" s="3"/>
+    </row>
+    <row r="553" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B553" s="3"/>
+    </row>
+    <row r="554" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B554" s="3"/>
+    </row>
+    <row r="555" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B555" s="3"/>
+    </row>
+    <row r="556" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B556" s="3"/>
+    </row>
+    <row r="557" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B557" s="3"/>
+    </row>
+    <row r="558" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B558" s="3"/>
+    </row>
+    <row r="559" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B559" s="3"/>
+    </row>
+    <row r="560" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B560" s="3"/>
+    </row>
+    <row r="561" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B561" s="3"/>
+    </row>
+    <row r="562" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B562" s="3"/>
+    </row>
+    <row r="563" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B563" s="3"/>
+    </row>
+    <row r="564" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B564" s="3"/>
+    </row>
+    <row r="565" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B565" s="3"/>
+    </row>
+    <row r="566" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B566" s="3"/>
+    </row>
+    <row r="567" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B567" s="3"/>
+    </row>
+    <row r="568" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B568" s="3"/>
+    </row>
+    <row r="569" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B569" s="3"/>
+    </row>
+    <row r="570" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B570" s="3"/>
+    </row>
+    <row r="571" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B571" s="3"/>
+    </row>
+    <row r="572" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B572" s="3"/>
+    </row>
+    <row r="573" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B573" s="3"/>
+    </row>
+    <row r="574" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B574" s="3"/>
+    </row>
+    <row r="575" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B575" s="3"/>
+    </row>
+    <row r="576" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B576" s="3"/>
+    </row>
+    <row r="577" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B577" s="3"/>
+    </row>
+    <row r="578" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B578" s="3"/>
+    </row>
+    <row r="579" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B579" s="3"/>
+    </row>
+    <row r="580" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B580" s="3"/>
+    </row>
+    <row r="581" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B581" s="3"/>
+    </row>
+    <row r="582" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B582" s="3"/>
+    </row>
+    <row r="583" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B583" s="3"/>
+    </row>
+    <row r="584" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B584" s="3"/>
+    </row>
+    <row r="585" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B585" s="3"/>
+    </row>
+    <row r="586" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B586" s="3"/>
+    </row>
+    <row r="587" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B587" s="3"/>
+    </row>
+    <row r="588" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B588" s="3"/>
+    </row>
+    <row r="589" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B589" s="3"/>
+    </row>
+    <row r="590" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B590" s="3"/>
+    </row>
+    <row r="591" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B591" s="3"/>
+    </row>
+    <row r="592" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B592" s="3"/>
+    </row>
+    <row r="593" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B593" s="3"/>
+    </row>
+    <row r="594" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B594" s="3"/>
+    </row>
+    <row r="595" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B595" s="3"/>
+    </row>
+    <row r="596" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B596" s="3"/>
+    </row>
+    <row r="597" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B597" s="3"/>
+    </row>
+    <row r="598" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B598" s="3"/>
+    </row>
+    <row r="599" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B599" s="3"/>
+    </row>
+    <row r="600" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B600" s="3"/>
+    </row>
+    <row r="601" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B601" s="3"/>
+    </row>
+    <row r="602" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B602" s="3"/>
+    </row>
+    <row r="603" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B603" s="3"/>
+    </row>
+    <row r="604" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B604" s="3"/>
+    </row>
+    <row r="605" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B605" s="3"/>
+    </row>
+    <row r="606" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B606" s="3"/>
+    </row>
+    <row r="607" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B607" s="3"/>
+    </row>
+    <row r="608" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B608" s="3"/>
+    </row>
+    <row r="609" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B609" s="3"/>
+    </row>
+    <row r="610" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B610" s="3"/>
+    </row>
+    <row r="611" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B611" s="3"/>
+    </row>
+    <row r="612" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B612" s="3"/>
+    </row>
+    <row r="613" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B613" s="3"/>
+    </row>
+    <row r="614" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B614" s="3"/>
+    </row>
+    <row r="615" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B615" s="3"/>
+    </row>
+    <row r="616" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B616" s="3"/>
+    </row>
+    <row r="617" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B617" s="3"/>
+    </row>
+    <row r="618" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B618" s="3"/>
+    </row>
+    <row r="619" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B619" s="3"/>
+    </row>
+    <row r="620" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B620" s="3"/>
+    </row>
+    <row r="621" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B621" s="3"/>
+    </row>
+    <row r="622" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B622" s="3"/>
+    </row>
+    <row r="623" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B623" s="3"/>
+    </row>
+    <row r="624" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B624" s="3"/>
+    </row>
+    <row r="625" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B625" s="3"/>
+    </row>
+    <row r="626" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B626" s="3"/>
+    </row>
+    <row r="627" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B627" s="3"/>
+    </row>
+    <row r="628" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B628" s="3"/>
+    </row>
+    <row r="629" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B629" s="3"/>
+    </row>
+    <row r="630" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B630" s="3"/>
+    </row>
+    <row r="631" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B631" s="3"/>
+    </row>
+    <row r="632" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B632" s="3"/>
+    </row>
+    <row r="633" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B633" s="3"/>
+    </row>
+    <row r="634" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B634" s="3"/>
+    </row>
+    <row r="635" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B635" s="3"/>
+    </row>
+    <row r="636" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B636" s="3"/>
+    </row>
+    <row r="637" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B637" s="3"/>
+    </row>
+    <row r="638" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B638" s="3"/>
+    </row>
+    <row r="639" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B639" s="3"/>
+    </row>
+    <row r="640" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B640" s="3"/>
+    </row>
+    <row r="641" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B641" s="3"/>
+    </row>
+    <row r="642" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B642" s="3"/>
+    </row>
+    <row r="643" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B643" s="3"/>
+    </row>
+    <row r="644" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B644" s="3"/>
+    </row>
+    <row r="645" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B645" s="3"/>
+    </row>
+    <row r="646" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B646" s="3"/>
+    </row>
+    <row r="647" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B647" s="3"/>
+    </row>
+    <row r="648" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B648" s="3"/>
+    </row>
+    <row r="649" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B649" s="3"/>
+    </row>
+    <row r="650" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B650" s="3"/>
+    </row>
+    <row r="651" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B651" s="3"/>
+    </row>
+    <row r="652" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B652" s="3"/>
+    </row>
+    <row r="653" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B653" s="3"/>
+    </row>
+    <row r="654" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B654" s="3"/>
+    </row>
+    <row r="655" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B655" s="3"/>
+    </row>
+    <row r="656" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B656" s="3"/>
+    </row>
+    <row r="657" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B657" s="3"/>
+    </row>
+    <row r="658" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B658" s="3"/>
+    </row>
+    <row r="659" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B659" s="3"/>
+    </row>
+    <row r="660" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B660" s="3"/>
+    </row>
+    <row r="661" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B661" s="3"/>
+    </row>
+    <row r="662" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B662" s="3"/>
+    </row>
+    <row r="663" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B663" s="3"/>
+    </row>
+    <row r="664" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B664" s="3"/>
+    </row>
+    <row r="665" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B665" s="3"/>
+    </row>
+    <row r="666" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B666" s="3"/>
+    </row>
+    <row r="667" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B667" s="3"/>
+    </row>
+    <row r="668" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B668" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <legacyDrawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="unknownStateType" error="Please define the StateType before using it here." xr:uid="{16EB0063-BB5A-5C43-A02D-D43AF0EAAFB9}">
+          <x14:formula1>
+            <xm:f>'1_StateTypes'!$A:$A</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:D218</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Unknown SensorType" xr:uid="{CD53E918-EBA0-D045-A260-BABC98B0DF08}">
+          <x14:formula1>
+            <xm:f>SensorTypes!$A:$A</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B668</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="5"/>
+    <col min="1" max="1" width="8.83203125" style="5"/>
     <col min="2" max="2" width="31" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" customWidth="1"/>
-    <col min="5" max="5" width="18.44140625" customWidth="1"/>
+    <col min="5" max="5" width="18.5" customWidth="1"/>
     <col min="6" max="6" width="28" customWidth="1"/>
     <col min="7" max="7" width="42.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2"/>
     </row>
-    <row r="3" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3"/>
     </row>
-    <row r="4" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4"/>
     </row>
-    <row r="5" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5"/>
     </row>
-    <row r="6" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6"/>
     </row>
-    <row r="7" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7"/>
     </row>
-    <row r="8" spans="1:11" s="6" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" s="6" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8"/>
       <c r="B8"/>
       <c r="C8"/>
@@ -774,228 +5866,285 @@
       <c r="F8"/>
       <c r="G8"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G11" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C595" xr:uid="{C498CBAF-9C9A-6C4C-ABAD-C35EAB699B17}">
+      <formula1>"causes, enables, prevents"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D595" xr:uid="{CD9CAE3E-5063-1740-B3CE-1334145A1528}">
+      <formula1>"overlaps, before"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E595" xr:uid="{12C2F65E-DDFE-D944-83A4-3FF453246D7D}">
+      <formula1>"parentPlatform, siblingPlatform, samePlatform"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <legacyDrawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Unknown StateType" xr:uid="{3E1BC39E-AFCA-7447-B012-9577908299AE}">
+          <x14:formula1>
+            <xm:f>'1_StateTypes'!$A:$A</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B595 F2:F595</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FFFF0000"/>
-  </sheetPr>
-  <dimension ref="A1:E34"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="30.33203125" customWidth="1"/>
-    <col min="2" max="2" width="31" customWidth="1"/>
-    <col min="3" max="3" width="28.6640625" customWidth="1"/>
-    <col min="4" max="4" width="54.33203125" customWidth="1"/>
-    <col min="6" max="6" width="19.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" s="4"/>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B34" s="7"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100DE058F8930E0E241B4560415FE1909FD" ma:contentTypeVersion="13" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="c6bffe89e109856986e4a153dc9c9910">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e9ad02b1-1808-4f55-81c1-02da346030c9" xmlns:ns3="c4d4e922-8223-4f42-92be-35e8d7f6a6aa" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3655badd60cf411d5bfbcddb7e8975c" ns2:_="" ns3:_="">
+    <xsd:import namespace="e9ad02b1-1808-4f55-81c1-02da346030c9"/>
+    <xsd:import namespace="c4d4e922-8223-4f42-92be-35e8d7f6a6aa"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e9ad02b1-1808-4f55-81c1-02da346030c9" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="10" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="11" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Bildmarkierungen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="1a14e36f-e084-4b04-bba6-548b1473dca1" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="18" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="19" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c4d4e922-8223-4f42-92be-35e8d7f6a6aa" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b185ff23-afac-42ac-b771-e913aa125b30}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="c4d4e922-8223-4f42-92be-35e8d7f6a6aa">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Inhaltstyp"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titel"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FFC5E0B4"/>
-  </sheetPr>
-  <dimension ref="A1:E20"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="28.33203125" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" customWidth="1"/>
-    <col min="4" max="4" width="28.6640625" customWidth="1"/>
-    <col min="5" max="5" width="58.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-    </row>
-    <row r="3" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-    </row>
-    <row r="4" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="3"/>
-    </row>
-    <row r="5" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="3"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="3"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="3"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="3"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="3"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="3"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="3"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="3"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-    </row>
-    <row r="20" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FFC5E0B4"/>
-  </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="13.6640625" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="15.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C3" s="3"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C4" s="3"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C5" s="3"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C6" s="3"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C7" s="3"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C8" s="3"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C9" s="3"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C10" s="3"/>
-    </row>
-    <row r="14" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="3"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E49F44B-A41E-465B-AAE6-BCCE8904B251}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="e9ad02b1-1808-4f55-81c1-02da346030c9"/>
+    <ds:schemaRef ds:uri="c4d4e922-8223-4f42-92be-35e8d7f6a6aa"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9021D77D-0171-444A-8359-A9F86F12F6AA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/infrastructure/knowledgebase/SystemData.xlsx
+++ b/infrastructure/knowledgebase/SystemData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\user1\sense\use-case-template\infrastructure\knowledgebase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1DCFDD2-506C-4909-B590-18496EBD7201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C053CD42-5709-4A81-8DDC-C814A3154197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="608" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="608" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlatformTypes" sheetId="1" r:id="rId1"/>
@@ -35,9 +35,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
@@ -210,7 +207,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="71">
   <si>
     <t>PlatformType</t>
   </si>
@@ -347,24 +344,6 @@
     <t>WithinBounds</t>
   </si>
   <si>
-    <t>Spike</t>
-  </si>
-  <si>
-    <t>amplitude1</t>
-  </si>
-  <si>
-    <t>amplitude2</t>
-  </si>
-  <si>
-    <t>slope1</t>
-  </si>
-  <si>
-    <t>slope2</t>
-  </si>
-  <si>
-    <t>width</t>
-  </si>
-  <si>
     <t>RiseTime</t>
   </si>
   <si>
@@ -426,6 +405,21 @@
   </si>
   <si>
     <t>ExampleStateType2</t>
+  </si>
+  <si>
+    <t>StableTime</t>
+  </si>
+  <si>
+    <t>maximum_delta</t>
+  </si>
+  <si>
+    <t>stable_time</t>
+  </si>
+  <si>
+    <t>CustomDefinition</t>
+  </si>
+  <si>
+    <t>implemented_in</t>
   </si>
 </sst>
 </file>
@@ -551,7 +545,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -573,16 +567,17 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Explanatory Text" xfId="1" builtinId="53"/>
@@ -670,9 +665,7 @@
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Schreiberhuber, Katrin" id="{CE6926BB-C9BE-8A48-9527-C0157D9F0173}" userId="S::katrin.schreiberhuber@wu.ac.at::a8bbfc8c-fdf4-4b40-89d7-e571648d1de5" providerId="AD"/>
-</personList>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -848,14 +841,6 @@
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="B1" dT="2024-08-05T14:54:41.70" personId="{CE6926BB-C9BE-8A48-9527-C0157D9F0173}" id="{09D8B89D-83C7-0A4D-A20A-A968FD3B7817}">
-    <text>Added as there was no connetion between eventTypes and sensors yet.</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
@@ -878,7 +863,7 @@
     </row>
     <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -917,7 +902,7 @@
     </row>
     <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -985,10 +970,10 @@
     </row>
     <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -3049,10 +3034,10 @@
     </row>
     <row r="2" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C2" t="b">
         <v>1</v>
@@ -3061,10 +3046,10 @@
     </row>
     <row r="3" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C3" t="b">
         <v>0</v>
@@ -3246,82 +3231,82 @@
         <v>17</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
       <c r="G2" s="11" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="O2" s="10" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F3" t="s">
         <v>30</v>
@@ -3329,14 +3314,12 @@
       <c r="G3" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="13" t="s">
-        <v>65</v>
+      <c r="H3" t="s">
+        <v>59</v>
       </c>
       <c r="I3">
         <v>1</v>
       </c>
-      <c r="K3" s="13"/>
-      <c r="N3" s="13"/>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="4"/>
@@ -3372,29 +3355,29 @@
           </x14:formula1>
           <xm:sqref>E3:E1048576</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3CF3A043-EA1C-4F42-937C-8B04B72FFA8D}">
+          <x14:formula1>
+            <xm:f>PlatformTypes!$A:$A</xm:f>
+          </x14:formula1>
+          <xm:sqref>D2:D1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{7F5B68FC-7714-4D02-B319-4ACA1D309FCB}">
+          <x14:formula1>
+            <xm:f>IF(H3="SensorValue",SensorTypes!$A:$A,SensorTypes!$Z:$Z)</xm:f>
+          </x14:formula1>
+          <xm:sqref>O3:O1048576 I3:I1048576 L3:L1048576</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4A86B01A-D006-4896-87A4-6C2FD7644D5A}">
           <x14:formula1>
             <xm:f>SignalProperties!$A:$A</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3CF3A043-EA1C-4F42-937C-8B04B72FFA8D}">
-          <x14:formula1>
-            <xm:f>PlatformTypes!$A:$A</xm:f>
-          </x14:formula1>
-          <xm:sqref>D2:D1048576</xm:sqref>
-        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{69C42B8B-2E42-4221-A6F7-F81194B80C62}">
           <x14:formula1>
             <xm:f>_xlfn.XLOOKUP($F3,SignalProperties!$A:$A,SignalProperties!$B:$K)</xm:f>
           </x14:formula1>
-          <xm:sqref>M3:M1048576 G3:G1048576 J3:J1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{7F5B68FC-7714-4D02-B319-4ACA1D309FCB}">
-          <x14:formula1>
-            <xm:f>IF(H3="SensorValue",SensorTypes!$A:$A,SensorTypes!$Z:$Z)</xm:f>
-          </x14:formula1>
-          <xm:sqref>O3:O1048576 I3:I1048576 L3:L1048576</xm:sqref>
+          <xm:sqref>M3:M1048576 J3:J1048576 G3:G1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3404,7 +3387,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5824542-7FEF-412D-B84A-5B5499A18F79}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.21875" customWidth="1"/>
@@ -3518,36 +3501,35 @@
       <c r="C6" t="s">
         <v>47</v>
       </c>
-      <c r="D6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F6" t="s">
-        <v>50</v>
-      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" t="s">
-        <v>55</v>
+      <c r="A8" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -3556,6 +3538,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100DE058F8930E0E241B4560415FE1909FD" ma:contentTypeVersion="13" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="c6bffe89e109856986e4a153dc9c9910">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e9ad02b1-1808-4f55-81c1-02da346030c9" xmlns:ns3="c4d4e922-8223-4f42-92be-35e8d7f6a6aa" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3655badd60cf411d5bfbcddb7e8975c" ns2:_="" ns3:_="">
     <xsd:import namespace="e9ad02b1-1808-4f55-81c1-02da346030c9"/>
@@ -3762,16 +3753,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9021D77D-0171-444A-8359-A9F86F12F6AA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E49F44B-A41E-465B-AAE6-BCCE8904B251}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3788,12 +3778,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9021D77D-0171-444A-8359-A9F86F12F6AA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>